--- a/Documents/聲調對照表.xlsx
+++ b/Documents/聲調對照表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\Piau-Im\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087B2D14-9C45-4C0D-A8B4-DA1AAF0E1727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813532A9-4786-48D7-BA0B-47A127CE69AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" autoFilterDateGrouping="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" firstSheet="3" activeTab="7" autoFilterDateGrouping="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="拚音聲調對照表" sheetId="1" r:id="rId1"/>
@@ -2468,7 +2468,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2919,6 +2919,12 @@
     <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -15012,6 +15018,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="env"/>
@@ -15366,6 +15373,43 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="0" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="3">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{C6CB2EB7-B2EC-48EA-B531-1F9C61CA7A4C}">
+  <we:reference id="wa200007447" version="1.1.6.7" store="zh-TW" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200007447" version="1.1.6.7" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
+<file path=xl/webextensions/webextension2.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{51FD2E8E-AF3A-4B4D-A368-A363DC4D3ED2}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;9afece23-b455-4bf7-80b3-57cfbba5c921&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8264B7F8-EC6F-425C-A778-2C680D504D26}">
   <dimension ref="B2:AF30"/>
@@ -17669,7 +17713,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="65.25">
+    <row r="3" spans="2:9" ht="50.25">
       <c r="B3" s="18" t="s">
         <v>26</v>
       </c>
@@ -17696,7 +17740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="65.25">
+    <row r="4" spans="2:9" ht="50.25">
       <c r="B4" s="19" t="s">
         <v>23</v>
       </c>
@@ -17723,7 +17767,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="65.25">
+    <row r="5" spans="2:9" ht="50.25">
       <c r="B5" s="18" t="s">
         <v>19</v>
       </c>
@@ -17750,7 +17794,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="65.25">
+    <row r="6" spans="2:9" ht="50.25">
       <c r="B6" s="19" t="s">
         <v>9</v>
       </c>
@@ -17777,7 +17821,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="65.25">
+    <row r="7" spans="2:9" ht="50.25">
       <c r="B7" s="18" t="s">
         <v>15</v>
       </c>
@@ -17804,7 +17848,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="65.25">
+    <row r="8" spans="2:9" ht="50.25">
       <c r="B8" s="19" t="s">
         <v>7</v>
       </c>
@@ -17830,7 +17874,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="65.25">
+    <row r="9" spans="2:9" ht="50.25">
       <c r="B9" s="18" t="s">
         <v>3</v>
       </c>
@@ -17930,7 +17974,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="2:10" ht="65.25">
+    <row r="3" spans="2:10" ht="59.25">
       <c r="B3" s="18" t="s">
         <v>26</v>
       </c>
@@ -17960,7 +18004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="65.25">
+    <row r="4" spans="2:10" ht="59.25">
       <c r="B4" s="19" t="s">
         <v>23</v>
       </c>
@@ -17990,7 +18034,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:10" ht="65.25">
+    <row r="5" spans="2:10" ht="59.25">
       <c r="B5" s="18" t="s">
         <v>19</v>
       </c>
@@ -18020,7 +18064,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="65.25">
+    <row r="6" spans="2:10" ht="59.25">
       <c r="B6" s="19" t="s">
         <v>9</v>
       </c>
@@ -18050,7 +18094,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="65.25">
+    <row r="7" spans="2:10" ht="59.25">
       <c r="B7" s="18" t="s">
         <v>15</v>
       </c>
@@ -18080,7 +18124,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:10" ht="65.25">
+    <row r="8" spans="2:10" ht="59.25">
       <c r="B8" s="19" t="s">
         <v>7</v>
       </c>
@@ -18109,7 +18153,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="2:10" ht="65.25">
+    <row r="9" spans="2:10" ht="59.25">
       <c r="B9" s="18" t="s">
         <v>3</v>
       </c>
@@ -23061,7 +23105,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75AC180E-22C7-41E3-9B1C-02C96E708532}">
-  <dimension ref="B2:O18"/>
+  <dimension ref="B2:P18"/>
   <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="4.125" customWidth="1"/>
@@ -23072,9 +23116,10 @@
     <col min="7" max="8" width="14.75" customWidth="1"/>
     <col min="9" max="9" width="15.375" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="12" max="12" width="13.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="25.5">
+    <row r="2" spans="2:16" ht="25.5">
       <c r="B2" s="13" t="s">
         <v>199</v>
       </c>
@@ -23101,375 +23146,407 @@
         <v>204</v>
       </c>
     </row>
-    <row r="3" spans="2:15" ht="57.75">
+    <row r="3" spans="2:16" ht="57.75">
       <c r="B3" s="42">
+        <v>0</v>
+      </c>
+      <c r="C3" s="40">
+        <v>2</v>
+      </c>
+      <c r="D3" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="E3" s="39" t="s">
+        <v>208</v>
+      </c>
+      <c r="F3" s="45">
+        <v>7</v>
+      </c>
+      <c r="G3" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="H3" s="44" t="s">
+        <v>211</v>
+      </c>
+      <c r="I3" s="44" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+030A",4))), "h"), "")</f>
+        <v>åh</v>
+      </c>
+      <c r="J3" s="44" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("a", F3)</f>
+        <v>a7</v>
+      </c>
+      <c r="L3" s="99" t="str">
+        <f xml:space="preserve"> RIGHT(M3,6)</f>
+        <v>U+0301</v>
+      </c>
+      <c r="M3" s="150" t="s">
+        <v>185</v>
+      </c>
+      <c r="N3" s="99">
+        <f xml:space="preserve"> IFERROR( HEX2DEC(RIGHT(M3,4)), "")</f>
+        <v>769</v>
+      </c>
+      <c r="O3" s="99" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT(M3,4)))), "")</f>
+        <v>ó</v>
+      </c>
+      <c r="P3" s="99" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("t", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT(M3,4))), "ng"), "")</f>
+        <v>tóng</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="57.75">
+      <c r="B4" s="42">
         <v>1</v>
       </c>
-      <c r="C3" s="40">
+      <c r="C4" s="40">
         <v>44</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D4" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E4" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="45" t="s">
+      <c r="F4" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="38" t="s">
+      <c r="G4" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="44" t="s">
+      <c r="H4" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="I3" s="44" t="str">
+      <c r="I4" s="44" t="str">
         <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("t", "o", "ng"), "")</f>
         <v>tong</v>
       </c>
-      <c r="J3" s="44" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("tong", F3)</f>
+      <c r="J4" s="44" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("tong", F4)</f>
         <v>tong;</v>
       </c>
-      <c r="L3" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="M3" s="35">
-        <f xml:space="preserve"> IFERROR( HEX2DEC(RIGHT(L3,4)), "")</f>
-        <v>769</v>
-      </c>
-      <c r="N3" s="35" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT(L3,4)))), "")</f>
-        <v>ó</v>
-      </c>
-      <c r="O3" s="35" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("t", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT(L3,4))), "ng"), "")</f>
-        <v>tóng</v>
+      <c r="L4" s="99" t="str">
+        <f t="shared" ref="L4:L10" si="0" xml:space="preserve"> RIGHT(M4,6)</f>
+        <v>U+0300</v>
+      </c>
+      <c r="M4" s="150" t="s">
+        <v>186</v>
+      </c>
+      <c r="N4" s="99">
+        <f t="shared" ref="N4:N10" si="1" xml:space="preserve"> IFERROR( HEX2DEC(RIGHT(M4,4)), "")</f>
+        <v>768</v>
+      </c>
+      <c r="O4" s="99" t="str">
+        <f t="shared" ref="O4:O10" si="2" xml:space="preserve"> IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT(M4,4)))), "")</f>
+        <v>ò</v>
+      </c>
+      <c r="P4" s="99" t="str">
+        <f t="shared" ref="P4:P10" si="3" xml:space="preserve"> IFERROR( _xlfn.CONCAT("t", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT(M4,4))), "ng"), "")</f>
+        <v>tòng</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="57.75">
-      <c r="B4" s="42">
+    <row r="5" spans="2:16" ht="57.75">
+      <c r="B5" s="42">
         <v>2</v>
       </c>
-      <c r="C4" s="40">
+      <c r="C5" s="40">
         <v>53</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D5" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E5" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="45" t="s">
+      <c r="F5" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="38" t="s">
+      <c r="G5" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="44" t="s">
+      <c r="H5" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="44" t="str">
+      <c r="I5" s="44" t="str">
         <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("t", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0301",4))), "ng"), "")</f>
         <v>tóng</v>
       </c>
-      <c r="J4" s="44" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("tong", F4)</f>
+      <c r="J5" s="44" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("tong", F5)</f>
         <v>tong\</v>
       </c>
-      <c r="L4" s="33" t="s">
-        <v>186</v>
-      </c>
-      <c r="M4" s="35">
-        <f t="shared" ref="M4:M10" si="0" xml:space="preserve"> IFERROR( HEX2DEC(RIGHT(L4,4)), "")</f>
-        <v>768</v>
-      </c>
-      <c r="N4" s="35" t="str">
-        <f t="shared" ref="N4:N10" si="1" xml:space="preserve"> IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT(L4,4)))), "")</f>
-        <v>ò</v>
-      </c>
-      <c r="O4" s="35" t="str">
-        <f t="shared" ref="O4:O10" si="2" xml:space="preserve"> IFERROR( _xlfn.CONCAT("t", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT(L4,4))), "ng"), "")</f>
-        <v>tòng</v>
+      <c r="L5" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>U+030D</v>
+      </c>
+      <c r="M5" s="151" t="s">
+        <v>121</v>
+      </c>
+      <c r="N5" s="99">
+        <f t="shared" si="1"/>
+        <v>781</v>
+      </c>
+      <c r="O5" s="99" t="str">
+        <f t="shared" si="2"/>
+        <v>o̍</v>
+      </c>
+      <c r="P5" s="99" t="str">
+        <f t="shared" si="3"/>
+        <v>to̍ng</v>
       </c>
     </row>
-    <row r="5" spans="2:15" ht="57.75">
-      <c r="B5" s="42">
+    <row r="6" spans="2:16" ht="57.75">
+      <c r="B6" s="42">
         <v>3</v>
       </c>
-      <c r="C5" s="40">
+      <c r="C6" s="40">
         <v>21</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="D6" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="39" t="s">
+      <c r="E6" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="45" t="s">
+      <c r="F6" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="38" t="s">
+      <c r="G6" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="44" t="s">
+      <c r="H6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="I5" s="44" t="str">
+      <c r="I6" s="44" t="str">
         <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("t", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0300",4))), "ng"), "")</f>
         <v>tòng</v>
       </c>
-      <c r="J5" s="44" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("tong", F5)</f>
+      <c r="J6" s="44" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("tong", F6)</f>
         <v>tong_</v>
       </c>
-      <c r="L5" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="M5" s="35">
+      <c r="L6" s="99" t="str">
         <f t="shared" si="0"/>
-        <v>781</v>
-      </c>
-      <c r="N5" s="35" t="str">
+        <v>U+0302</v>
+      </c>
+      <c r="M6" s="150" t="s">
+        <v>120</v>
+      </c>
+      <c r="N6" s="99">
         <f t="shared" si="1"/>
-        <v>o̍</v>
-      </c>
-      <c r="O5" s="35" t="str">
+        <v>770</v>
+      </c>
+      <c r="O6" s="99" t="str">
         <f t="shared" si="2"/>
-        <v>to̍ng</v>
+        <v>ô</v>
+      </c>
+      <c r="P6" s="99" t="str">
+        <f t="shared" si="3"/>
+        <v>tông</v>
       </c>
     </row>
-    <row r="6" spans="2:15" ht="57.75">
-      <c r="B6" s="42">
+    <row r="7" spans="2:16" ht="57.75">
+      <c r="B7" s="42">
         <v>4</v>
       </c>
-      <c r="C6" s="40">
+      <c r="C7" s="40">
         <v>32</v>
       </c>
-      <c r="D6" s="39" t="s">
+      <c r="D7" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="E7" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="45" t="s">
+      <c r="F7" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="G6" s="38" t="s">
+      <c r="G7" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="44" t="s">
+      <c r="H7" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="I6" s="44" t="str">
+      <c r="I7" s="44" t="str">
         <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("t", "o", "k"), "")</f>
         <v>tok</v>
       </c>
-      <c r="J6" s="44" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("tok", F6)</f>
+      <c r="J7" s="44" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("tok", F7)</f>
         <v>tok[</v>
       </c>
-      <c r="L6" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="M6" s="35">
+      <c r="L7" s="99" t="str">
         <f t="shared" si="0"/>
-        <v>770</v>
-      </c>
-      <c r="N6" s="35" t="str">
+        <v>U+030C</v>
+      </c>
+      <c r="M7" s="150" t="s">
+        <v>177</v>
+      </c>
+      <c r="N7" s="99">
         <f t="shared" si="1"/>
-        <v>ô</v>
-      </c>
-      <c r="O6" s="35" t="str">
+        <v>780</v>
+      </c>
+      <c r="O7" s="99" t="str">
         <f t="shared" si="2"/>
-        <v>tông</v>
+        <v>ǒ</v>
+      </c>
+      <c r="P7" s="99" t="str">
+        <f t="shared" si="3"/>
+        <v>tǒng</v>
       </c>
     </row>
-    <row r="7" spans="2:15" ht="57.75">
-      <c r="B7" s="42">
+    <row r="8" spans="2:16" ht="57.75">
+      <c r="B8" s="42">
         <v>5</v>
       </c>
-      <c r="C7" s="40">
+      <c r="C8" s="40">
         <v>13</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D8" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="39" t="s">
+      <c r="E8" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="45" t="s">
+      <c r="F8" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G8" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="44" t="s">
+      <c r="H8" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="I7" s="44" t="str">
+      <c r="I8" s="44" t="str">
         <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("t", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0302",4))), "ng"), "")</f>
         <v>tông</v>
       </c>
-      <c r="J7" s="44" t="str">
-        <f t="shared" ref="J7:J8" si="3" xml:space="preserve"> _xlfn.CONCAT("tong", F7)</f>
+      <c r="J8" s="44" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("tong", F8)</f>
         <v>tong/</v>
       </c>
-      <c r="L7" s="33" t="s">
-        <v>177</v>
-      </c>
-      <c r="M7" s="35">
+      <c r="L8" s="99" t="str">
         <f t="shared" si="0"/>
-        <v>780</v>
-      </c>
-      <c r="N7" s="35" t="str">
+        <v>U+0304</v>
+      </c>
+      <c r="M8" s="150" t="s">
+        <v>178</v>
+      </c>
+      <c r="N8" s="99">
         <f t="shared" si="1"/>
-        <v>ǒ</v>
-      </c>
-      <c r="O7" s="35" t="str">
+        <v>772</v>
+      </c>
+      <c r="O8" s="99" t="str">
         <f t="shared" si="2"/>
-        <v>tǒng</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15" ht="57.75">
-      <c r="B8" s="42">
-        <v>7</v>
-      </c>
-      <c r="C8" s="40">
-        <v>22</v>
-      </c>
-      <c r="D8" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="44" t="s">
-        <v>205</v>
-      </c>
-      <c r="I8" s="44" t="str">
+        <v>ō</v>
+      </c>
+      <c r="P8" s="99" t="str">
         <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("t", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0304",4))), "ng"), "")</f>
         <v>tōng</v>
       </c>
-      <c r="J8" s="44" t="str">
-        <f t="shared" si="3"/>
-        <v>tong-</v>
-      </c>
-      <c r="L8" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="M8" s="35">
-        <f t="shared" si="0"/>
-        <v>772</v>
-      </c>
-      <c r="N8" s="35" t="str">
-        <f t="shared" si="1"/>
-        <v>ō</v>
-      </c>
-      <c r="O8" s="35" t="str">
+    </row>
+    <row r="9" spans="2:16" ht="57.75">
+      <c r="B9" s="42">
+        <v>7</v>
+      </c>
+      <c r="C9" s="40">
+        <v>22</v>
+      </c>
+      <c r="D9" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="44" t="s">
+        <v>205</v>
+      </c>
+      <c r="I9" s="44" t="str">
         <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("t", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0304",4))), "ng"), "")</f>
         <v>tōng</v>
       </c>
+      <c r="J9" s="44" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("tong", F9)</f>
+        <v>tong-</v>
+      </c>
+      <c r="L9" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>U+030D</v>
+      </c>
+      <c r="M9" s="150" t="s">
+        <v>210</v>
+      </c>
+      <c r="N9" s="99">
+        <f t="shared" si="1"/>
+        <v>781</v>
+      </c>
+      <c r="O9" s="99" t="str">
+        <f t="shared" si="2"/>
+        <v>o̍</v>
+      </c>
+      <c r="P9" s="99" t="str">
+        <f t="shared" si="3"/>
+        <v>to̍ng</v>
+      </c>
     </row>
-    <row r="9" spans="2:15" ht="57.75">
-      <c r="B9" s="42">
+    <row r="10" spans="2:16" ht="57.75">
+      <c r="B10" s="42">
         <v>8</v>
       </c>
-      <c r="C9" s="40">
+      <c r="C10" s="40">
         <v>121</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D10" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="39" t="s">
+      <c r="E10" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="F9" s="45" t="s">
+      <c r="F10" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="38" t="s">
+      <c r="G10" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="H9" s="44" t="s">
+      <c r="H10" s="44" t="s">
         <v>206</v>
       </c>
-      <c r="I9" s="44" t="str">
+      <c r="I10" s="44" t="str">
         <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("t", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+030D",4))), "k"), "")</f>
         <v>to̍k</v>
       </c>
-      <c r="J9" s="44" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("tok", F9)</f>
+      <c r="J10" s="44" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("tok", F10)</f>
         <v>tok]</v>
       </c>
-      <c r="L9" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="M9" s="35">
+      <c r="L10" s="99" t="str">
         <f t="shared" si="0"/>
-        <v>781</v>
-      </c>
-      <c r="N9" s="35" t="str">
+        <v>U+030B</v>
+      </c>
+      <c r="M10" s="150" t="s">
+        <v>122</v>
+      </c>
+      <c r="N10" s="99">
         <f t="shared" si="1"/>
-        <v>o̍</v>
-      </c>
-      <c r="O9" s="35" t="str">
+        <v>779</v>
+      </c>
+      <c r="O10" s="99" t="str">
         <f t="shared" si="2"/>
-        <v>to̍ng</v>
+        <v>ő</v>
+      </c>
+      <c r="P10" s="99" t="str">
+        <f t="shared" si="3"/>
+        <v>tőng</v>
       </c>
     </row>
-    <row r="10" spans="2:15" ht="57.75">
-      <c r="B10" s="42">
-        <v>0</v>
-      </c>
-      <c r="C10" s="40">
-        <v>2</v>
-      </c>
-      <c r="D10" s="39" t="s">
-        <v>207</v>
-      </c>
-      <c r="E10" s="39" t="s">
-        <v>208</v>
-      </c>
-      <c r="F10" s="45">
-        <v>7</v>
-      </c>
-      <c r="G10" s="38" t="s">
-        <v>209</v>
-      </c>
-      <c r="H10" s="44" t="s">
-        <v>211</v>
-      </c>
-      <c r="I10" s="44" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+030A",4))), "h"), "")</f>
-        <v>åh</v>
-      </c>
-      <c r="J10" s="44" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("a", F10)</f>
-        <v>a7</v>
-      </c>
-      <c r="L10" s="33" t="s">
-        <v>122</v>
-      </c>
-      <c r="M10" s="35">
-        <f t="shared" si="0"/>
-        <v>779</v>
-      </c>
-      <c r="N10" s="35" t="str">
-        <f t="shared" si="1"/>
-        <v>ő</v>
-      </c>
-      <c r="O10" s="35" t="str">
-        <f t="shared" si="2"/>
-        <v>tőng</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" ht="57.75">
+    <row r="14" spans="2:16" ht="57.75">
       <c r="B14" s="42">
         <v>6</v>
       </c>
@@ -23489,7 +23566,7 @@
       </c>
       <c r="J14" s="44"/>
     </row>
-    <row r="15" spans="2:15" ht="57.75">
+    <row r="15" spans="2:16" ht="57.75">
       <c r="B15" s="42">
         <v>9</v>
       </c>
@@ -23532,18 +23609,21 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:J10">
+    <sortCondition ref="B10"/>
+  </sortState>
   <mergeCells count="1">
     <mergeCell ref="H2:I2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="L3" r:id="rId1" display="https://zi-hi.com/sp/uni/0301" xr:uid="{0A4706D1-84DC-4182-A96A-35027C3F443C}"/>
-    <hyperlink ref="L4" r:id="rId2" display="https://zi-hi.com/sp/uni/0300" xr:uid="{CA7CE6B9-ACB2-4BD4-8CCD-9F323F16DB19}"/>
-    <hyperlink ref="L6" r:id="rId3" display="https://zi-hi.com/sp/uni/0302" xr:uid="{F51ED1B0-F464-4664-949A-2BF6E8D92207}"/>
-    <hyperlink ref="L7" r:id="rId4" display="https://zi-hi.com/sp/uni/030C" xr:uid="{A13388BA-C8A0-49CD-AD7D-92E78949E725}"/>
-    <hyperlink ref="L8" r:id="rId5" display="https://zi-hi.com/sp/uni/0304" xr:uid="{7DCF3A33-F3D8-4D15-8566-6580CE02AB86}"/>
-    <hyperlink ref="L9" r:id="rId6" display="https://zi-hi.com/sp/uni/030D" xr:uid="{89C45CD8-4919-45C7-BEF4-7CAB5797EF54}"/>
-    <hyperlink ref="L10" r:id="rId7" display="https://zi-hi.com/sp/uni/030B" xr:uid="{EC0523CB-79C1-4D03-88B1-0D58C6FCDA18}"/>
+    <hyperlink ref="M3" r:id="rId1" display="https://zi-hi.com/sp/uni/0301" xr:uid="{0A4706D1-84DC-4182-A96A-35027C3F443C}"/>
+    <hyperlink ref="M4" r:id="rId2" display="https://zi-hi.com/sp/uni/0300" xr:uid="{CA7CE6B9-ACB2-4BD4-8CCD-9F323F16DB19}"/>
+    <hyperlink ref="M6" r:id="rId3" display="https://zi-hi.com/sp/uni/0302" xr:uid="{F51ED1B0-F464-4664-949A-2BF6E8D92207}"/>
+    <hyperlink ref="M7" r:id="rId4" display="https://zi-hi.com/sp/uni/030C" xr:uid="{A13388BA-C8A0-49CD-AD7D-92E78949E725}"/>
+    <hyperlink ref="M8" r:id="rId5" display="https://zi-hi.com/sp/uni/0304" xr:uid="{7DCF3A33-F3D8-4D15-8566-6580CE02AB86}"/>
+    <hyperlink ref="M9" r:id="rId6" display="https://zi-hi.com/sp/uni/030D" xr:uid="{89C45CD8-4919-45C7-BEF4-7CAB5797EF54}"/>
+    <hyperlink ref="M10" r:id="rId7" display="https://zi-hi.com/sp/uni/030B" xr:uid="{EC0523CB-79C1-4D03-88B1-0D58C6FCDA18}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId8"/>
@@ -23588,7 +23668,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="65.25">
+    <row r="3" spans="2:12" ht="57.75">
       <c r="B3" s="36" t="s">
         <v>26</v>
       </c>
@@ -23621,7 +23701,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="65.25">
+    <row r="4" spans="2:12" ht="57.75">
       <c r="B4" s="37" t="s">
         <v>23</v>
       </c>
@@ -23652,7 +23732,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="65.25">
+    <row r="5" spans="2:12" ht="57.75">
       <c r="B5" s="36" t="s">
         <v>19</v>
       </c>
@@ -23683,7 +23763,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="65.25">
+    <row r="6" spans="2:12" ht="57.75">
       <c r="B6" s="37" t="s">
         <v>9</v>
       </c>
@@ -23714,7 +23794,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="65.25">
+    <row r="7" spans="2:12" ht="57.75">
       <c r="B7" s="36" t="s">
         <v>15</v>
       </c>
@@ -23745,7 +23825,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="65.25">
+    <row r="8" spans="2:12" ht="57.75">
       <c r="B8" s="37" t="s">
         <v>7</v>
       </c>
@@ -23775,7 +23855,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="65.25">
+    <row r="9" spans="2:12" ht="57.75">
       <c r="B9" s="36" t="s">
         <v>3</v>
       </c>
